--- a/Assets/Resources/Configs/HexConfig.xlsx
+++ b/Assets/Resources/Configs/HexConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6D255B-96B8-48A1-AF2B-961DE179F0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF7F102-BD3E-447D-965B-C5769DA94B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,18 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>全能龙魂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OmnipotentDragonSoul</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得3个随机龙魂。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>WisdomOfTime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -220,23 +208,6 @@
   </si>
   <si>
     <t>Hex_Skill_Border</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>棱彩蛋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PrismaticEgg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每击杀200个敌人可以孵化出一个棱彩锻造器和一次刷新机会。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每击杀200个敌人可以孵化出一个棱彩锻造器和一次刷新机会。
-当前击杀数：{0:D}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -246,26 +217,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Hex_Shop_Border</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连锁闪电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChainLightning</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对敌人造成伤害时还会对其附近最近的2个敌人造成相当于这次伤害30%的真实伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hex_Explosion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>属性叠属性叠属性！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -278,38 +229,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>巨人杀手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GiantKiller</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体型变小，获得移动速度，并基于敌人体型大于你的程度造成额外伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hex_Speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>慢炖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hex_Fire</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SlowStew</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每秒对附近的敌人施加一层可无限叠加的灼烧，这个效果受益于你的最大生命值。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>踢踏舞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -322,17 +241,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对敌人造成伤害时还会对其附近500码内最近的2个敌人造成相当于这次伤害30%的真实伤害。
-当前已造成额外伤害：{0:F1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在你攻击时发射一根次级弩箭，造成40%伤害和40%效能的攻击特效。获得25%总攻击速度。
-当前已造成额外伤害：{0:F1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体型减小75%，获得30%总移动速度加成，敌人的体型每比你大5%，则对其造成2%额外真实伤害。
 当前已造成额外伤害：{0:F1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -402,10 +311,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每秒对附近的敌人施加一层可无限叠加的灼烧，持续5秒，每秒造成你0.35%最大生命值的魔法伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>你的攻击为你提供5移动速度，可无限叠加，持续5秒。获得{0:P1}=(10%&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;)的攻击速度。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -418,9 +323,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得1000金币并降低所有锻造器的价格。
-棱彩锻造器数量：-1000
-传说锻造器数量：-500
+    <t>获得1000金币并降低所有锻造器的价格，但是所有装备的出售价格降低至原价格的40%。
+传说锻造器数量：-1000
 属性锻造器数量：-100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -791,7 +695,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -803,54 +707,39 @@
       <c r="E1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>17</v>
+      <c r="F1" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>83</v>
+      <c r="N1" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -862,47 +751,32 @@
       <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
+      <c r="F2" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>84</v>
+      <c r="N2" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -948,21 +822,6 @@
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
     </row>
@@ -971,7 +830,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
@@ -980,49 +839,34 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>60</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1030,90 +874,75 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>31</v>
@@ -1122,84 +951,54 @@
         <v>57</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/Assets/Resources/Configs/HexConfig.xlsx
+++ b/Assets/Resources/Configs/HexConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF7F102-BD3E-447D-965B-C5769DA94B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CD0784-0D7C-4299-84EE-70B117CE8B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -324,7 +324,7 @@
   </si>
   <si>
     <t>获得1000金币并降低所有锻造器的价格，但是所有装备的出售价格降低至原价格的40%。
-传说锻造器数量：-1000
+传说锻造器数量：-750
 属性锻造器数量：-100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/Assets/Resources/Configs/HexConfig.xlsx
+++ b/Assets/Resources/Configs/HexConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CD0784-0D7C-4299-84EE-70B117CE8B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A30B18-3EC0-4D57-A90E-B68C398AB1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="162">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -301,12 +301,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>你的技能命中会施加燃烧效果，持续5秒，每秒造成
-{0:F0}=6+(1.2%&lt;color=#C97BFF&gt;法术强度&lt;/color&gt;)+(2.8%&lt;color=#FF8A00&gt;攻击力&lt;/color&gt;)&lt;color=#C97BFF&gt;魔法伤害&lt;/color&gt;。
-此灼烧效果可无限叠加，你的所有灼烧效果会使你的所有基础技能的冷却时间减少0.5秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>你的技能可以暴击，获得{0:P0}=(25%+4.5%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;)暴击几率。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -326,6 +320,379 @@
     <t>获得1000金币并降低所有锻造器的价格，但是所有装备的出售价格降低至原价格的40%。
 传说锻造器数量：-750
 属性锻造器数量：-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>质变：棱彩阶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QualitativeChange_Prismatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1个随机棱彩阶强化符文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性叠属性！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttributesAttributes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3个属性锻造器！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>急急小子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RapidBoy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;，相当于你的150%&lt;sprite="Attributes" name="AbilityHasteIcon"&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得{0:P0}&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;=（150%&lt;sprite="Attributes" name="AbilityHasteIcon"&gt;）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hex_Speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShootingWizard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的攻击造成相当于你100%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;的额外&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的攻击造成相当于你100%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;的额外&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;
+已造成伤害：{0:F1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神射法师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿针引线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得20%物理穿透和法术穿透</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hex_Explosion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedlesAndThreads</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血习性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vampires</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接二连三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TwoAndThree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每第三次攻击，你的攻击特效会额外触发一次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵魂虹吸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得25%暴击几率和12%生命偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电打击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的技能命中会施加燃烧效果，持续5秒，每秒造成&lt;color=#C97BFF&gt;
+{0:F0}=6+(1.2%&lt;color=#C97BFF&gt;法术强度&lt;/color&gt;)+(2.8%&lt;color=#FF8A00&gt;攻击力&lt;/color&gt;)魔法伤害&lt;/color&gt;。
+此灼烧效果可无限叠加，你的所有灼烧效果会使你的所有基础技能的冷却时间减少0.5秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得20%总&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;。
+当你的攻击速度达到400%时，造成额外&lt;color=#C97BFF&gt;{0:F0}=（20+5%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;）法术伤害的攻击特效&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得20%总&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;。
+当你的攻击速度达到400%时，造成额外&lt;color=#C97BFF&gt;{0:F0}=（20+5%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;）法术伤害的攻击特效&lt;/color&gt;
+已造成伤害：{1:F1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务：海牛阿福的勇士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoulSuck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightningStrike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Task_Warrior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务：击杀50个敌人
+奖励：金铲铲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超凡邪恶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExcellentEvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在你用技能命中敌人时永久获得1&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在你用技能命中敌人时永久获得1&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;。
+已获得法术强度：{0:F0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关键暴击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得50%暴击几率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CrucialCritical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>循环往复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recycle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得75技能急速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真正的残暴之力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TrulyBrutalPower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BrutalPower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Silver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残暴（温柔）之力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QualitativeChange_Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>质变：黄金阶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1个随机黄金阶强化符文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火爆甩卖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HotSell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立刻售出你的所有装备并且获取相当于他们100%原价的金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得25攻击力，10技能急速和5物理穿透</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得40攻击力，20技能急速和15物理穿透</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hex_Shop_Border</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法转物理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理转魔法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APToAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADToAP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将法术强度转化为攻击力，获得15%总攻击力加成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将攻击力转化为法术强度，获得15%总法术强度加成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将每0.6攻击力转化为1法术强度，获得15%总法术强度加成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将每1法术强度转化为0.6攻击力，获得15%总攻击力加成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BigPower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得20%总攻击力加成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attributes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得2个属性锻造器！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>职业杀手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MajorKiller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌人时额外获得20%金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重量级打击手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zangief</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的攻击造成相当于你3.5%最大生命值的额外物理伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的攻击造成相当于你3.5%最大生命值的额外物理伤害
+已造成伤害：{0:F1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Typhoon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>练腿日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PracticeLeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得50移动速度和幽灵状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的攻击会对一个额外目标发射一根弩箭，这个弩箭会造成30%额外伤害并施加攻击特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得30%全能吸血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渴血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThirstingForBlood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得15%全能吸血</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -685,13 +1052,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U95"/>
+  <dimension ref="A1:AN95"/>
   <sheetFormatPr defaultColWidth="43.125" defaultRowHeight="61.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="43.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -734,8 +1101,86 @@
       <c r="N1" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN1" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -778,8 +1223,86 @@
       <c r="N2" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AN2" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -822,15 +1345,91 @@
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-    </row>
-    <row r="4" spans="1:21" ht="221.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" ht="221.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
@@ -857,7 +1456,7 @@
         <v>48</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>55</v>
@@ -868,19 +1467,97 @@
       <c r="N4" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>20</v>
@@ -895,13 +1572,13 @@
         <v>64</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>56</v>
@@ -910,10 +1587,88 @@
         <v>20</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -956,8 +1711,86 @@
       <c r="N6" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -1000,48 +1833,126 @@
       <c r="N7" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>

--- a/Assets/Resources/Configs/HexConfig.xlsx
+++ b/Assets/Resources/Configs/HexConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A30B18-3EC0-4D57-A90E-B68C398AB1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD636A1F-35A8-4F8B-8569-D55A9F2CAF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="153">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -351,22 +351,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>急急小子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RapidBoy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;，相当于你的150%&lt;sprite="Attributes" name="AbilityHasteIcon"&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得{0:P0}&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;=（150%&lt;sprite="Attributes" name="AbilityHasteIcon"&gt;）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hex_Speed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -417,10 +401,6 @@
   </si>
   <si>
     <t>TwoAndThree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每第三次攻击，你的攻击特效会额外触发一次。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -443,11 +423,6 @@
   </si>
   <si>
     <t>获得20%总&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;。
-当你的攻击速度达到400%时，造成额外&lt;color=#C97BFF&gt;{0:F0}=（20+5%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;）法术伤害的攻击特效&lt;/color&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得20%总&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;。
 当你的攻击速度达到400%时，造成额外&lt;color=#C97BFF&gt;{0:F0}=（20+5%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;）法术伤害的攻击特效&lt;/color&gt;
 已造成伤害：{1:F1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -571,38 +546,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>魔法转物理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理转魔法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>APToAD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADToAP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>将法术强度转化为攻击力，获得15%总攻击力加成。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>将攻击力转化为法术强度，获得15%总法术强度加成。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>将每0.6攻击力转化为1法术强度，获得15%总法术强度加成。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>将每1法术强度转化为0.6攻击力，获得15%总攻击力加成。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -676,10 +619,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>你的攻击会对一个额外目标发射一根弩箭，这个弩箭会造成30%额外伤害并施加攻击特效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获得30%全能吸血</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -693,6 +632,35 @@
   </si>
   <si>
     <t>获得15%全能吸血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的攻击会对原目标发射一根弩箭，这个弩箭会造成30%额外伤害和攻击特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的攻击会对原目标发射一根弩箭，这个弩箭会造成30%额外伤害和攻击特效
+已造成伤害：{0:F1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每第三次攻击，发射一根弩箭造成200%的额外伤害和攻击特效。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每第三次攻击，发射一根弩箭造成200%的额外伤害和攻击特效。
+已造成伤害：{0:F1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得20%总&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;。
+当你的攻击速度达到400%时，造成额外&lt;color=#C97BFF&gt;20+5%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;法术伤害的攻击特效&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务：击杀50个敌人
+奖励：金铲铲
+当前已击杀：{0:F0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1052,13 +1020,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN95"/>
+  <dimension ref="A1:AK95"/>
   <sheetFormatPr defaultColWidth="43.125" defaultRowHeight="61.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="43.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1101,86 +1069,77 @@
       <c r="N1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="4" t="s">
         <v>72</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>83</v>
+      <c r="R1" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>94</v>
+      <c r="U1" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="Z1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB1" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AA1" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="AC1" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AF1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>134</v>
+      <c r="AF1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="AH1" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AI1" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK1" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1223,86 +1182,77 @@
       <c r="N2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="4" t="s">
         <v>71</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>86</v>
+      <c r="Q2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="S2" s="4" t="s">
         <v>87</v>
       </c>
       <c r="T2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="W2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>107</v>
+      <c r="X2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="Z2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="AA2" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="AB2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC2" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="AC2" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AD2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE2" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="AG2" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="AH2" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM2" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="AN2" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1385,46 +1335,37 @@
         <v>73</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40" ht="221.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" ht="221.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1480,73 +1421,64 @@
         <v>84</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>100</v>
       </c>
       <c r="X4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="Y4" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="Z4" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AE4" s="2" t="s">
         <v>127</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AL4" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AM4" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AN4" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1557,7 +1489,7 @@
         <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>20</v>
@@ -1599,76 +1531,67 @@
         <v>81</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="U5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="W5" s="2" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="X5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y5" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="Y5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="Z5" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="AA5" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="AE5" s="2" t="s">
         <v>127</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AL5" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AM5" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AN5" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1717,14 +1640,14 @@
       <c r="P6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>89</v>
+      <c r="R6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>24</v>
@@ -1732,65 +1655,56 @@
       <c r="U6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="V6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="X6" s="1" t="s">
+      <c r="Z6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z6" s="1" t="s">
+      <c r="AE6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AH6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI6" s="2" t="s">
-        <v>28</v>
+      <c r="AI6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="AK6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AL6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AM6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -1839,120 +1753,111 @@
       <c r="P7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>27</v>
+      <c r="Q7" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="S7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W7" s="1" t="s">
+      <c r="W7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y7" s="1" t="s">
+      <c r="Y7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="AB7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AC7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG7" s="1" t="s">
-        <v>25</v>
+      <c r="AF7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AH7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="AJ7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AN7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:40" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
